--- a/test_codes/百度表格-修复版_11.xlsx
+++ b/test_codes/百度表格-修复版_11.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/test_codes/百度表格-修复版_11.xlsx
+++ b/test_codes/百度表格-修复版_11.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -436,615 +436,443 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>(人民币百万元，百分比除外)</t>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>1个月以内</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>1至3个月</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr"/>
+          <t>3至12个月</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2025年6月30日
+1至5年</t>
+        </is>
+      </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>非生息</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>合计</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2024年
-12月31日</t>
-        </is>
-      </c>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>现金及存放中央银行款项</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>3,093,680</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2024年
-9月30日</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2024年
-6月30日</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2024年
-3月31日</t>
+          <t>14,111</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>255,040</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>3,362,831</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>可用资本（数额）</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
+          <t>存放同业及其他金融机构款项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>249,455</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>27,509</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>112,721</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>15,558</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>5,675</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>410,918</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>拆出资金</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>核心一级资本净额</t>
+          <t>215,711</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,165,549</t>
+          <t>86,358</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,124,043</t>
+          <t>150,096</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,038,387</t>
+          <t>15,951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,045,754</t>
+          <t>1,219</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,126</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>472,461</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>一级资本净额</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3,324,424</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3,322,954</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3,237,254</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3,245,824</t>
+          <t>衍生金融资产</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,680</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,680</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>买入返售金融资产</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>资本净额</t>
+          <t>1,521,048</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,303,263</t>
+          <t>12,284</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,285,564</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,175,087</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,175,290</t>
+          <t>16,807</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,132</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,554,271</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>风险加权资产（数额）</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>发放贷款和垫款</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>4,067,775</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4,861,912</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15,418,100</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1,113,993</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>249,563</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>52,658</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,764,001</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>以公允价值计量且其变动计入当期损益的
+金融资产</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>风险加权资产合计</t>
+          <t>8,818</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21,854,590</t>
+          <t>42,853</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22,150,555</t>
+          <t>101,155</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21,690,492</t>
+          <t>44,493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,586,165</t>
+          <t>159,886</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>163,953</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>521,158</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4a</t>
+          <t>以摊余成本计量的债权投资</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>风险加权资产合计（应用资本
-底线前)</t>
+          <t>151,837</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,854,590</t>
+          <t>317,704</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,150,555</t>
+          <t>673,262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,690,492</t>
+          <t>2,801,737</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,586,165</t>
+          <t>6,245,152</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>159,276</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10,348,968</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>资本充足率</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+          <t>以公允价值计量且其变动计入其他综合收益的
+其他债权和其他权益工具投资</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>172,622</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>320,325</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>745,198</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,558,808</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>727,272</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>46,032</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,570,257</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>核心一级资本充足率(%)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>14.10</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14.11</t>
+          <t>其他金融资产</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>268,508</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>268,508</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>5a</t>
+          <t>金融资产总额</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>核心一级资本充足率(%)
-(应用资本底线前)</t>
+          <t>9,480,946</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>5,668,945</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>17,231,450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>5,550,540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>一级资本充足率(%)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6a</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>一级资本充足率(%)（应用
-资本底线前)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>资本充足率(%)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>19.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>7a</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>资本充足率(%)（应用资本
-底线前)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>其他各级资本要求</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>储备资本要求(%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>逆周期资本要求(%)</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>全球系统重要性银行或国内系
-统重要性银行附加资本要求
-(%)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>其他各级资本要求(%)
-(8+9+10)</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>12
-杠杆率</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>满足最低资本要求后的可用核
-心一级资本净额占风险加权资
-产的比例(%)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>9.21</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>8.92</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>9.04</t>
+          <t>7,383,092</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,001,080</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>46,316,053</t>
         </is>
       </c>
     </row>
